--- a/outputs/daily/hr_rankings_2026-08-13.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-13.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>63.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1235,7 +1235,7 @@
         <v>55.6</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1249,39 +1249,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1502,7 +1498,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1744,7 +1740,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2138,7 +2134,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2380,7 +2376,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3404,7 +3400,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3646,7 +3642,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -4040,7 +4036,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4282,7 +4278,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -5297,24 +5293,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-08-14T02:10:00Z</t>
@@ -5322,31 +5318,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5360,26 +5356,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>36.7</v>
+        <v>36.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>54.8</v>
+        <v>35.4</v>
       </c>
       <c r="R16" t="n">
         <v>55.6</v>
       </c>
       <c r="S16" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>46.5</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5387,42 +5383,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5439,12 +5431,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5454,12 +5446,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5469,102 +5461,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>101.4213</t>
+          <t>99.849</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.4336</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3294</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>73.27</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1855</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5615,32 +5607,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5650,12 +5642,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5664,7 +5656,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5678,26 +5670,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>50.4</v>
+        <v>36.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.5</v>
+        <v>54.8</v>
       </c>
       <c r="R17" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="S17" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5740,7 +5732,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5757,132 +5749,132 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>102.1801</t>
+          <t>101.4213</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3553</t>
+          <t>0.3294</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5892,7 +5884,7 @@
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL17" t="inlineStr">
@@ -5907,12 +5899,12 @@
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr"/>
@@ -5933,27 +5925,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5963,22 +5955,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -5996,26 +5988,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>36.2</v>
+        <v>50.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="R18" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="S18" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>46.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6033,7 +6025,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -6075,7 +6067,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -6085,122 +6077,122 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.849</t>
+          <t>102.1801</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.4336</t>
+          <t>0.475</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.3553</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1855</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>241 deg</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6210,7 +6202,7 @@
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL18" t="inlineStr">
@@ -6225,12 +6217,12 @@
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr"/>
@@ -6276,7 +6268,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6518,7 +6510,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6871,27 +6863,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6901,26 +6893,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6934,26 +6926,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>33.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="R21" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="S21" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>81.7</v>
+        <v>56.2</v>
       </c>
       <c r="V21" t="n">
         <v>50</v>
@@ -6971,7 +6963,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -7013,12 +7005,12 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -7033,7 +7025,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -7043,102 +7035,102 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>98.539</t>
+          <t>102.0363</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4441</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>0.1588</t>
+          <t>0.1985</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.3328</t>
+          <t>0.3451</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>41.99</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.2254</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>241 deg</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -7148,7 +7140,7 @@
       </c>
       <c r="BK21" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL21" t="inlineStr">
@@ -7163,12 +7155,12 @@
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr"/>
@@ -7189,56 +7181,56 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>50.5</v>
+        <v>49.8</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -7252,26 +7244,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>50.1</v>
+        <v>42.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>13.5</v>
+        <v>35.4</v>
       </c>
       <c r="R22" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="S22" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U22" t="n">
-        <v>56.2</v>
+        <v>18</v>
       </c>
       <c r="V22" t="n">
         <v>50</v>
@@ -7279,39 +7271,35 @@
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7331,27 +7319,27 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -7361,102 +7349,102 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>102.0363</t>
+          <t>100.4673</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.4441</t>
+          <t>0.4824</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>0.1985</t>
+          <t>0.1923</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.3451</t>
+          <t>0.3689</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>41.99</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>0.2254</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -7466,7 +7454,7 @@
       </c>
       <c r="BK22" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL22" t="inlineStr">
@@ -7481,12 +7469,12 @@
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr"/>
@@ -7825,12 +7813,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -7850,12 +7838,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -7874,7 +7862,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -7888,11 +7876,11 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>42.4</v>
+        <v>41.4</v>
       </c>
       <c r="Q24" t="n">
         <v>35.4</v>
@@ -7901,13 +7889,13 @@
         <v>55.6</v>
       </c>
       <c r="S24" t="n">
-        <v>92.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>50</v>
@@ -7915,39 +7903,35 @@
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7967,12 +7951,12 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -7982,12 +7966,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -7997,67 +7981,67 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>100.4673</t>
+          <t>100.8738</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.4824</t>
+          <t>0.4221</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>0.1923</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.3689</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>30.01</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -8092,7 +8076,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -8168,7 +8152,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8410,7 +8394,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -10347,27 +10331,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>666139</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -10377,26 +10361,26 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -10414,22 +10398,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>41.4</v>
+        <v>34.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>35.4</v>
+        <v>50.8</v>
       </c>
       <c r="R32" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="S32" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T32" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V32" t="n">
         <v>50</v>
@@ -10447,7 +10431,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -10472,7 +10456,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr"/>
@@ -10494,7 +10478,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -10504,12 +10488,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -10519,102 +10503,102 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>38.83</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>100.8738</t>
+          <t>99.4278</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.4221</t>
+          <t>0.3868</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>30.01</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1404</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>241 deg</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
@@ -10624,7 +10608,7 @@
       </c>
       <c r="BK32" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL32" t="inlineStr">
@@ -10639,12 +10623,12 @@
       </c>
       <c r="BN32" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr"/>
@@ -10665,56 +10649,56 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>666139</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>45.8</v>
+        <v>45.6</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -10728,26 +10712,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>34.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>50.8</v>
+        <v>34.4</v>
       </c>
       <c r="R33" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="S33" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T33" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U33" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="V33" t="n">
         <v>50</v>
@@ -10755,42 +10739,38 @@
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr"/>
@@ -10807,12 +10787,12 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -10822,12 +10802,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -10837,102 +10817,102 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>99.4278</t>
+          <t>99.655</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3868</t>
+          <t>0.3886</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.3196</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.1404</t>
+          <t>0.1367</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
@@ -10942,7 +10922,7 @@
       </c>
       <c r="BK33" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL33" t="inlineStr">
@@ -10957,12 +10937,12 @@
       </c>
       <c r="BN33" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr"/>
@@ -11301,56 +11281,56 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>664761</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-13T23:30:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>671737</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -11364,26 +11344,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>23.7</v>
+        <v>29.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>34.4</v>
+        <v>46.8</v>
       </c>
       <c r="R35" t="n">
-        <v>55.6</v>
+        <v>42.6</v>
       </c>
       <c r="S35" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T35" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>10.8</v>
+        <v>29.4</v>
       </c>
       <c r="V35" t="n">
         <v>50</v>
@@ -11391,42 +11371,38 @@
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr"/>
@@ -11443,12 +11419,12 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
@@ -11458,12 +11434,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 6/19, 0 HR</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 17.6 HR allowed</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -11473,132 +11449,120 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>43.04</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>99.655</t>
+          <t>100.1087</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3886</t>
+          <t>0.3948</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1348</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.3196</t>
+          <t>0.3149</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>71.14</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>21.88</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.1367</t>
+          <t>0.1276</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1561</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK35" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL35" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="BM35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>MLB Stats API weather feed</t>
+        </is>
+      </c>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
       <c r="BN35" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO35" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Field of Dreams</t>
         </is>
       </c>
       <c r="BP35" t="inlineStr"/>
@@ -11619,27 +11583,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>664761</t>
+          <t>571771</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-13T23:30:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -11649,26 +11613,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>671737</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>44.6</v>
+        <v>44.3</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -11682,26 +11646,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>29.6</v>
+        <v>39.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>46.8</v>
+        <v>35.4</v>
       </c>
       <c r="R36" t="n">
-        <v>42.6</v>
+        <v>55.6</v>
       </c>
       <c r="S36" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U36" t="n">
-        <v>29.4</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>50</v>
@@ -11719,7 +11683,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -11740,7 +11704,7 @@
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr"/>
@@ -11757,12 +11721,12 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
@@ -11772,12 +11736,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 0 HR</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 17.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -11787,120 +11751,132 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>100.1087</t>
+          <t>99.5161</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3948</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>0.1348</t>
+          <t>0.1744</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.3149</t>
+          <t>0.3024</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>71.14</t>
+          <t>70.47</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.1276</t>
+          <t>0.2155</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>0.1561</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
         <is>
-          <t>MLB Stats API weather feed</t>
-        </is>
-      </c>
-      <c r="BK36" t="inlineStr"/>
-      <c r="BL36" t="inlineStr"/>
-      <c r="BM36" t="inlineStr"/>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL36" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="BM36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="BN36" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BO36" t="inlineStr">
         <is>
-          <t>Field of Dreams</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP36" t="inlineStr"/>
@@ -12239,12 +12215,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -12254,7 +12230,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -12264,7 +12240,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -12288,7 +12264,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -12302,11 +12278,11 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>34</v>
+        <v>19.2</v>
       </c>
       <c r="Q38" t="n">
         <v>35.4</v>
@@ -12315,55 +12291,49 @@
         <v>55.6</v>
       </c>
       <c r="S38" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T38" t="n">
+        <v>78</v>
+      </c>
+      <c r="U38" t="n">
+        <v>32</v>
+      </c>
+      <c r="V38" t="n">
         <v>50</v>
       </c>
-      <c r="U38" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="V38" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>57</v>
-      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12383,27 +12353,27 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 6/18 over last 7 games</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -12413,67 +12383,67 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>35.54</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>87.32</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>98.8348</t>
+          <t>98.1514</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3937</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>0.1563</t>
+          <t>0.1146</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.3461</t>
+          <t>0.3154</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>36.57</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>32.98</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.1588</t>
+          <t>0.1294</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -12508,7 +12478,7 @@
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr">
@@ -12542,56 +12512,16 @@
         </is>
       </c>
       <c r="BP38" t="inlineStr"/>
-      <c r="BQ38" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR38" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="BS38" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BT38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU38" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="BV38" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="BW38" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX38" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ38" t="inlineStr">
-        <is>
-          <t>Park/split help but hitter sheet not loud</t>
-        </is>
-      </c>
+      <c r="BQ38" t="inlineStr"/>
+      <c r="BR38" t="inlineStr"/>
+      <c r="BS38" t="inlineStr"/>
+      <c r="BT38" t="inlineStr"/>
+      <c r="BU38" t="inlineStr"/>
+      <c r="BV38" t="inlineStr"/>
+      <c r="BW38" t="inlineStr"/>
+      <c r="BX38" t="inlineStr"/>
+      <c r="BY38" t="inlineStr"/>
+      <c r="BZ38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -13235,12 +13165,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>571771</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -13260,12 +13190,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -13284,7 +13214,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -13298,11 +13228,11 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>39.7</v>
+        <v>34</v>
       </c>
       <c r="Q41" t="n">
         <v>35.4</v>
@@ -13311,55 +13241,51 @@
         <v>55.6</v>
       </c>
       <c r="S41" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T41" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V41" t="n">
-        <v>19.5</v>
+        <v>27.1</v>
       </c>
       <c r="W41" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -13379,27 +13305,27 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/12, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -13409,67 +13335,67 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>99.5161</t>
+          <t>98.8348</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>0.4164</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>0.1744</t>
+          <t>0.1563</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.3024</t>
+          <t>0.3461</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>70.47</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>32.98</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.2155</t>
+          <t>0.1588</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -13504,7 +13430,7 @@
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
@@ -13545,12 +13471,12 @@
       </c>
       <c r="BR41" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="BS41" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BT41" t="inlineStr">
@@ -13560,12 +13486,12 @@
       </c>
       <c r="BU41" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BV41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="BW41" t="inlineStr">
@@ -13575,17 +13501,17 @@
       </c>
       <c r="BX41" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="BY41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BZ41" t="inlineStr">
         <is>
-          <t>Tiny sample; park helps but not core parlay leg</t>
+          <t>Park/split help but hitter sheet not loud</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14754,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -15070,7 +14996,7 @@
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr">
@@ -15146,7 +15072,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -15388,7 +15314,7 @@
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr">
@@ -17340,7 +17266,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -17364,7 +17290,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>29.3</v>
+        <v>29.9</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -17378,7 +17304,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -17391,7 +17317,7 @@
         <v>55.6</v>
       </c>
       <c r="S54" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T54" t="n">
         <v>50</v>
@@ -17405,39 +17331,35 @@
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -17582,7 +17504,7 @@
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr">
@@ -18726,7 +18648,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -18750,7 +18672,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>63.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -18764,7 +18686,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -18777,7 +18699,7 @@
         <v>55.6</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -18791,39 +18713,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -18968,7 +18886,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -19044,7 +18962,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -19286,7 +19204,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -19680,7 +19598,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -19922,7 +19840,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -20946,7 +20864,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21188,7 +21106,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -21582,7 +21500,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21824,7 +21742,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -22839,24 +22757,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-08-14T02:10:00Z</t>
@@ -22864,31 +22782,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -22902,26 +22820,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>36.7</v>
+        <v>36.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>54.8</v>
+        <v>35.4</v>
       </c>
       <c r="R16" t="n">
         <v>55.6</v>
       </c>
       <c r="S16" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>46.5</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -22929,42 +22847,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -22981,12 +22895,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -22996,12 +22910,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -23011,102 +22925,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>101.4213</t>
+          <t>99.849</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.4336</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3294</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>73.27</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1855</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -23157,32 +23071,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23192,12 +23106,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -23206,7 +23120,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -23220,26 +23134,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>50.4</v>
+        <v>36.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.5</v>
+        <v>54.8</v>
       </c>
       <c r="R17" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="S17" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -23282,7 +23196,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -23299,132 +23213,132 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>102.1801</t>
+          <t>101.4213</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3553</t>
+          <t>0.3294</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -23434,7 +23348,7 @@
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL17" t="inlineStr">
@@ -23449,12 +23363,12 @@
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr"/>
@@ -23475,27 +23389,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -23505,22 +23419,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -23538,26 +23452,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>36.2</v>
+        <v>50.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="R18" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="S18" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>46.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -23575,7 +23489,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -23617,7 +23531,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -23627,122 +23541,122 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.849</t>
+          <t>102.1801</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.4336</t>
+          <t>0.475</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.3553</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1855</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>241 deg</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -23752,7 +23666,7 @@
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL18" t="inlineStr">
@@ -23767,12 +23681,12 @@
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr"/>
@@ -23818,7 +23732,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -24060,7 +23974,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -24413,27 +24327,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -24443,26 +24357,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -24476,26 +24390,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>33.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="R21" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="S21" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>81.7</v>
+        <v>56.2</v>
       </c>
       <c r="V21" t="n">
         <v>50</v>
@@ -24513,7 +24427,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -24555,12 +24469,12 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -24575,7 +24489,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -24585,102 +24499,102 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>98.539</t>
+          <t>102.0363</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4441</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>0.1588</t>
+          <t>0.1985</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.3328</t>
+          <t>0.3451</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>41.99</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.2254</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>241 deg</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -24690,7 +24604,7 @@
       </c>
       <c r="BK21" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL21" t="inlineStr">
@@ -24705,12 +24619,12 @@
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr"/>
